--- a/log_adeies.xlsx
+++ b/log_adeies.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5528,13 +5528,2413 @@
       <c r="F159" t="n">
         <v>1</v>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="H159" s="3" t="n">
+      <c r="G159" t="n">
+        <v>181</v>
+      </c>
+      <c r="H159" s="2" t="n">
         <v>46141</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:50</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ΣΚΙΚΟΥ</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ΣΠΥΡΙΔΟΥΛΑ</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ΠΕ11</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="n">
+        <v>536</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:50</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ΣΚΙΚΟΥ</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ΣΠΥΡΙΔΟΥΛΑ</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ΠΕ11</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" t="n">
+        <v>536</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:51</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>ΣΚΙΚΟΥ</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ΣΠΥΡΙΔΟΥΛΑ</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ΠΕ11</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" t="n">
+        <v>536</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:51</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ΣΚΙΚΟΥ</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ΣΠΥΡΙΔΟΥΛΑ</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ΠΕ11</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" t="n">
+        <v>536</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:51</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>ΣΚΙΚΟΥ</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ΣΠΥΡΙΔΟΥΛΑ</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ΠΕ11</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" t="n">
+        <v>536</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:53</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ΣΚΙΚΟΥ</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ΣΠΥΡΙΔΟΥΛΑ</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ΠΕ11</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" t="n">
+        <v>536</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:54</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ΣΚΙΚΟΥ</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ΣΠΥΡΙΔΟΥΛΑ</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ΠΕ11</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="n">
+        <v>536</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:54</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ΣΚΙΚΟΥ</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ΣΠΥΡΙΔΟΥΛΑ</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ΠΕ11</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" t="n">
+        <v>536</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:54</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ΣΚΙΚΟΥ</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ΣΠΥΡΙΔΟΥΛΑ</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ΠΕ11</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" t="n">
+        <v>536</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:55</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ΣΚΙΚΟΥ</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ΣΠΥΡΙΔΟΥΛΑ</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ΠΕ11</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" t="n">
+        <v>536</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:55</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ΣΚΙΚΟΥ</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ΣΠΥΡΙΔΟΥΛΑ</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ΠΕ11</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="n">
+        <v>536</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:55</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>ΣΚΙΚΟΥ</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ΣΠΥΡΙΔΟΥΛΑ</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ΠΕ11</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" t="n">
+        <v>536</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:59</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" t="n">
+        <v>536</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:59</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" t="n">
+        <v>536</v>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:59</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" t="n">
+        <v>536</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:59</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" t="n">
+        <v>536</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>02/07/2026 10:59</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" t="n">
+        <v>536</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:00</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" t="n">
+        <v>562</v>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:00</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" t="n">
+        <v>562</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:00</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" t="n">
+        <v>562</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:00</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" t="n">
+        <v>562</v>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:00</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" t="n">
+        <v>562</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:01</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="n">
+        <v>562</v>
+      </c>
+      <c r="H182" s="2" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:02</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="n">
+        <v>2</v>
+      </c>
+      <c r="G183" t="n">
+        <v>562</v>
+      </c>
+      <c r="H183" s="2" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:02</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="n">
+        <v>2</v>
+      </c>
+      <c r="G184" t="n">
+        <v>562</v>
+      </c>
+      <c r="H184" s="2" t="n">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:02</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" t="n">
+        <v>548</v>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:02</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="n">
+        <v>2</v>
+      </c>
+      <c r="G186" t="n">
+        <v>548</v>
+      </c>
+      <c r="H186" s="2" t="n">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:04</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>ΛΟΥΔΑΡΟ</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ΝΙΚΗΤΑ</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ΠΕ79</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="n">
+        <v>2</v>
+      </c>
+      <c r="G187" t="n">
+        <v>548</v>
+      </c>
+      <c r="H187" s="2" t="n">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:04</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ΛΟΥΔΑΡΟ</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ΝΙΚΗΤΑ</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ΠΕ79</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="n">
+        <v>2</v>
+      </c>
+      <c r="G188" t="n">
+        <v>548</v>
+      </c>
+      <c r="H188" s="2" t="n">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:05</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>ΛΟΥΔΑΡΟ</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ΝΙΚΗΤΑ</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ΠΕ79</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="n">
+        <v>2</v>
+      </c>
+      <c r="G189" t="n">
+        <v>548</v>
+      </c>
+      <c r="H189" s="2" t="n">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:05</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>ΛΟΥΔΑΡΟ</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ΝΙΚΗΤΑ</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ΠΕ79</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" t="n">
+        <v>548</v>
+      </c>
+      <c r="H190" s="2" t="n">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:05</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ΛΟΥΔΑΡΟ</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ΝΙΚΗΤΑ</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ΠΕ79</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" t="n">
+        <v>548</v>
+      </c>
+      <c r="H191" s="2" t="n">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:05</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>ΛΟΥΔΑΡΟ</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ΝΙΚΗΤΑ</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ΠΕ79</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" t="n">
+        <v>292</v>
+      </c>
+      <c r="H192" s="2" t="n">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:05</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>ΛΟΥΔΑΡΟ</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ΝΙΚΗΤΑ</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ΠΕ79</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" t="n">
+        <v>292</v>
+      </c>
+      <c r="H193" s="2" t="n">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:07</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>ΧΡΟΝΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ΔΗΜΗΤΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ΠΕ03</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="n">
+        <v>292</v>
+      </c>
+      <c r="H194" s="2" t="n">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:07</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ΧΡΟΝΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ΔΗΜΗΤΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ΠΕ03</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="n">
+        <v>292</v>
+      </c>
+      <c r="H195" s="2" t="n">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:07</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ΧΡΟΝΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ΔΗΜΗΤΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>ΠΕ03</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="n">
+        <v>292</v>
+      </c>
+      <c r="H196" s="2" t="n">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:07</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ΧΡΟΝΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ΔΗΜΗΤΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>ΠΕ03</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" t="n">
+        <v>292</v>
+      </c>
+      <c r="H197" s="2" t="n">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:08</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>ΧΡΟΝΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>ΔΗΜΗΤΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>ΠΕ03</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" t="n">
+        <v>292</v>
+      </c>
+      <c r="H198" s="2" t="n">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:08</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>ΧΡΟΝΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ΔΗΜΗΤΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ΠΕ03</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" t="n">
+        <v>292</v>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:08</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>ΧΡΟΝΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ΔΗΜΗΤΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ΠΕ03</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>535</v>
+      </c>
+      <c r="H200" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:08</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>ΧΡΟΝΟΠΟΥΛΟΣ</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ΔΗΜΗΤΡΙΟΣ</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ΠΕ03</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="n">
+        <v>535</v>
+      </c>
+      <c r="H201" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:10</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>ΣΤΑΜΟΥ</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ΜΑΡΙΝΑ</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="n">
+        <v>535</v>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:10</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ΣΤΑΜΟΥ</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ΜΑΡΙΝΑ</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" t="n">
+        <v>535</v>
+      </c>
+      <c r="H203" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:11</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>ΣΤΑΜΟΥ</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ΜΑΡΙΝΑ</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" t="n">
+        <v>535</v>
+      </c>
+      <c r="H204" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:11</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ΣΤΑΜΟΥ</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ΜΑΡΙΝΑ</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" t="n">
+        <v>535</v>
+      </c>
+      <c r="H205" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:11</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>ΣΤΑΜΟΥ</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ΜΑΡΙΝΑ</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="n">
+        <v>535</v>
+      </c>
+      <c r="H206" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:11</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>ΣΤΑΜΟΥ</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ΜΑΡΙΝΑ</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="n">
+        <v>539</v>
+      </c>
+      <c r="H207" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:11</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>ΣΤΑΜΟΥ</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ΜΑΡΙΝΑ</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="n">
+        <v>539</v>
+      </c>
+      <c r="H208" s="2" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:04</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ΣΙΔΕΡΗ</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ΧΡΙΣΤΙΝΑ</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" t="n">
+        <v>727</v>
+      </c>
+      <c r="H209" s="2" t="n">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:04</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ΣΙΔΕΡΗ</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ΧΡΙΣΤΙΝΑ</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" t="n">
+        <v>727</v>
+      </c>
+      <c r="H210" s="2" t="n">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:06</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" t="n">
+        <v>727</v>
+      </c>
+      <c r="H211" s="2" t="n">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:07</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" t="n">
+        <v>727</v>
+      </c>
+      <c r="H212" s="2" t="n">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:07</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="n">
+        <v>727</v>
+      </c>
+      <c r="H213" s="2" t="n">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:07</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="n">
+        <v>727</v>
+      </c>
+      <c r="H214" s="2" t="n">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:07</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" t="n">
+        <v>734</v>
+      </c>
+      <c r="H215" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:07</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" t="n">
+        <v>734</v>
+      </c>
+      <c r="H216" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:10</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" t="n">
+        <v>734</v>
+      </c>
+      <c r="H217" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:10</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" t="n">
+        <v>734</v>
+      </c>
+      <c r="H218" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:10</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" t="n">
+        <v>734</v>
+      </c>
+      <c r="H219" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:10</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" t="n">
+        <v>734</v>
+      </c>
+      <c r="H220" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:10</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" t="n">
+        <v>734</v>
+      </c>
+      <c r="H221" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:11</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" t="n">
+        <v>734</v>
+      </c>
+      <c r="H222" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:11</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="n">
+        <v>1</v>
+      </c>
+      <c r="G223" t="n">
+        <v>734</v>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:11</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" t="n">
+        <v>687</v>
+      </c>
+      <c r="H224" s="2" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:11</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ΤΑΣΣΙΑ</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ΓΕΩΡΓΙΟ</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>ΠΕ02</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" t="n">
+        <v>687</v>
+      </c>
+      <c r="H225" s="2" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:14</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" t="n">
+        <v>687</v>
+      </c>
+      <c r="H226" s="2" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:14</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" t="n">
+        <v>687</v>
+      </c>
+      <c r="H227" s="2" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:15</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" t="n">
+        <v>687</v>
+      </c>
+      <c r="H228" s="2" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:15</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" t="n">
+        <v>687</v>
+      </c>
+      <c r="H229" s="2" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:15</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" t="n">
+        <v>687</v>
+      </c>
+      <c r="H230" s="2" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:15</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" t="n">
+        <v>687</v>
+      </c>
+      <c r="H231" s="2" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:15</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="n">
+        <v>1</v>
+      </c>
+      <c r="G232" t="n">
+        <v>687</v>
+      </c>
+      <c r="H232" s="2" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:15</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="n">
+        <v>1</v>
+      </c>
+      <c r="G233" t="n">
+        <v>705</v>
+      </c>
+      <c r="H233" s="2" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>14/10/2026 12:15</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>ΣΤΑΘΟΠΟΥΛΟ</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>ΘΕΟΦΑΝΗ</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ΠΕ86</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="n">
+        <v>1</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="H234" s="3" t="n">
+        <v>46296</v>
       </c>
     </row>
   </sheetData>

--- a/log_adeies.xlsx
+++ b/log_adeies.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H234"/>
+  <dimension ref="A1:H238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7928,13 +7928,141 @@
       <c r="F234" t="n">
         <v>1</v>
       </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="H234" s="3" t="n">
+      <c r="G234" t="n">
+        <v>705</v>
+      </c>
+      <c r="H234" s="2" t="n">
         <v>46296</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>14/10/2026 13:15</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="n">
+        <v>1</v>
+      </c>
+      <c r="G235" t="n">
+        <v>734</v>
+      </c>
+      <c r="H235" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>14/10/2026 13:15</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="n">
+        <v>1</v>
+      </c>
+      <c r="G236" t="n">
+        <v>734</v>
+      </c>
+      <c r="H236" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>14/10/2026 13:25</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="n">
+        <v>1</v>
+      </c>
+      <c r="G237" t="n">
+        <v>734</v>
+      </c>
+      <c r="H237" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>14/10/2026 13:25</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="n">
+        <v>1</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="H238" s="3" t="n">
+        <v>46309</v>
       </c>
     </row>
   </sheetData>

--- a/log_adeies.xlsx
+++ b/log_adeies.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:H244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8056,12 +8056,204 @@
       <c r="F238" t="n">
         <v>1</v>
       </c>
-      <c r="G238" t="inlineStr">
+      <c r="G238" t="n">
+        <v>734</v>
+      </c>
+      <c r="H238" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>14/10/2026 13:45</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="n">
+        <v>1</v>
+      </c>
+      <c r="G239" t="n">
+        <v>734</v>
+      </c>
+      <c r="H239" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>14/10/2026 13:45</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="n">
+        <v>1</v>
+      </c>
+      <c r="G240" t="n">
+        <v>734</v>
+      </c>
+      <c r="H240" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>14/10/2026 13:45</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="n">
+        <v>1</v>
+      </c>
+      <c r="G241" t="n">
+        <v>734</v>
+      </c>
+      <c r="H241" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>14/10/2026 13:45</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="n">
+        <v>1</v>
+      </c>
+      <c r="G242" t="n">
+        <v>734</v>
+      </c>
+      <c r="H242" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>14/10/2026 13:45</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="n">
+        <v>1</v>
+      </c>
+      <c r="G243" t="n">
+        <v>734</v>
+      </c>
+      <c r="H243" s="2" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>14/10/2026 13:45</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>ΡΩΜΑΝΑ</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>ΕΛΕΝΗ</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>ΠΕ04.01</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="n">
+        <v>1</v>
+      </c>
+      <c r="G244" t="inlineStr">
         <is>
           <t>734</t>
         </is>
       </c>
-      <c r="H238" s="3" t="n">
+      <c r="H244" s="3" t="n">
         <v>46309</v>
       </c>
     </row>
